--- a/Evaluaciones/Proyectos/AvancesProyecto.xlsx
+++ b/Evaluaciones/Proyectos/AvancesProyecto.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EGCC\PortableGit\UPN_2026_2_DAS_26084\Evaluaciones\Proyectos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EC0A2D-A9A4-408B-AA97-DA53E4950DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AA4BF2-D42D-43B4-A383-772F3E017330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF5B7381-BB89-4A3B-89AE-E38281CF4A2F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BF5B7381-BB89-4A3B-89AE-E38281CF4A2F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Grupo04" sheetId="3" r:id="rId1"/>
-    <sheet name="Grupo05" sheetId="2" r:id="rId2"/>
-    <sheet name="Grupo01" sheetId="1" r:id="rId3"/>
+    <sheet name="Grupo01" sheetId="1" r:id="rId1"/>
+    <sheet name="Grupo08" sheetId="5" r:id="rId2"/>
+    <sheet name="Grupo04" sheetId="3" r:id="rId3"/>
+    <sheet name="Grupo05" sheetId="2" r:id="rId4"/>
+    <sheet name="Grupo06" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="6">
   <si>
     <t>Fecha</t>
   </si>
@@ -41,6 +43,14 @@
   <si>
     <t>Manejar un stock minimo por producto.
 Diferentes tipos de procesos de merma.</t>
+  </si>
+  <si>
+    <t>Capitulo 1
+Esta por analizar el manejo de concurrencia.</t>
+  </si>
+  <si>
+    <t>Capitulo 1
+¿Cómo se pretende manejar la prioridad de un ticket?</t>
   </si>
 </sst>
 </file>
@@ -558,7 +568,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -580,6 +590,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -955,6 +968,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0D1A38-C13B-495A-906B-18A508CE3C67}">
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="101" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>46268</v>
+      </c>
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98694BA7-6942-4C83-B803-5734AFED90D8}">
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="101" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>46275</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44CDD5BC-0771-42E7-A7FF-79705651E22C}">
   <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -980,7 +1363,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="8"/>
       <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1140,7 +1523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB58B093-F056-4B7F-A1D0-9240F7F2DD68}">
   <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1326,8 +1709,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0D1A38-C13B-495A-906B-18A508CE3C67}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203043E4-7BE9-4943-A633-9EFE513CAB82}">
   <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1343,11 +1726,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46268</v>
+        <v>46275</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="7" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>

--- a/Evaluaciones/Proyectos/AvancesProyecto.xlsx
+++ b/Evaluaciones/Proyectos/AvancesProyecto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EGCC\PortableGit\UPN_2026_2_DAS_26084\Evaluaciones\Proyectos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AA4BF2-D42D-43B4-A383-772F3E017330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99871A1-75E4-4DB0-897B-729FFFF0270C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BF5B7381-BB89-4A3B-89AE-E38281CF4A2F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{BF5B7381-BB89-4A3B-89AE-E38281CF4A2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Grupo01" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
   <si>
     <t>Fecha</t>
   </si>
@@ -51,6 +51,10 @@
   <si>
     <t>Capitulo 1
 ¿Cómo se pretende manejar la prioridad de un ticket?</t>
+  </si>
+  <si>
+    <t>Prototipos - Avance.
+Mejorar colores, son muy oscuros.</t>
   </si>
 </sst>
 </file>
@@ -1734,9 +1738,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2"/>
+    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
